--- a/artfynd/A 47392-2022 artfynd.xlsx
+++ b/artfynd/A 47392-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47392-2022 artfynd.xlsx
+++ b/artfynd/A 47392-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2141,6 +2141,113 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123451766</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97324</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Branaflons SO-spets, i granskog med dike 520 m OSO om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>503506</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7008293</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19F2c13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47392-2022 artfynd.xlsx
+++ b/artfynd/A 47392-2022 artfynd.xlsx
@@ -2146,7 +2146,7 @@
         <v>123451766</v>
       </c>
       <c r="B14" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 47392-2022 artfynd.xlsx
+++ b/artfynd/A 47392-2022 artfynd.xlsx
@@ -2146,7 +2146,7 @@
         <v>123451766</v>
       </c>
       <c r="B14" t="n">
-        <v>97333</v>
+        <v>97350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 47392-2022 artfynd.xlsx
+++ b/artfynd/A 47392-2022 artfynd.xlsx
@@ -2146,7 +2146,7 @@
         <v>123451766</v>
       </c>
       <c r="B14" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 47392-2022 artfynd.xlsx
+++ b/artfynd/A 47392-2022 artfynd.xlsx
@@ -2146,7 +2146,7 @@
         <v>123451766</v>
       </c>
       <c r="B14" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 47392-2022 artfynd.xlsx
+++ b/artfynd/A 47392-2022 artfynd.xlsx
@@ -2146,7 +2146,7 @@
         <v>123451766</v>
       </c>
       <c r="B14" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 47392-2022 artfynd.xlsx
+++ b/artfynd/A 47392-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101818220</v>
+        <v>103956827</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brana Ö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503518.8313935641</v>
+        <v>503492</v>
       </c>
       <c r="R2" t="n">
-        <v>7008271.427278268</v>
+        <v>7008418</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Område med minst 10 stånd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,76 +775,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Via Johan Råghall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102887208</v>
+        <v>109531173</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brana Ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503503.6427510905</v>
+        <v>503496</v>
       </c>
       <c r="R3" t="n">
-        <v>7008527.248445525</v>
+        <v>7008416</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,27 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Endast räknat blommande/överblommade ex.</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,88 +861,66 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Thomas Stålhandske, Pär Hedberg, Pontus Wallén, Johan Staaf, Erik Lundmark, Eva Romell, Sarah J Leander, Lisa Linck, Maria Gylle, Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102887209</v>
+        <v>109531176</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brana Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503500.0590693383</v>
+        <v>503489</v>
       </c>
       <c r="R4" t="n">
-        <v>7008498.819147208</v>
+        <v>7008429</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,27 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Endast räknat blommande/överblommade ex.</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,73 +958,59 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Thomas Stålhandske, Pär Hedberg, Pontus Wallén, Johan Staaf, Erik Lundmark, Eva Romell, Sarah J Leander, Lisa Linck, Maria Gylle, Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102887214</v>
+        <v>109531177</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1111,13 +1019,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503561.1438669401</v>
+        <v>503491</v>
       </c>
       <c r="R5" t="n">
-        <v>7008417.669112943</v>
+        <v>7008411</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1141,27 +1049,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Endast räknat blommande/överblommade ex.</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,27 +1070,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Thomas Stålhandske, Pär Hedberg, Pontus Wallén, Johan Staaf, Erik Lundmark, Eva Romell, Sarah J Leander, Lisa Linck, Maria Gylle, Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102887194</v>
+        <v>109531184</v>
       </c>
       <c r="B6" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,16 +1093,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1222,20 +1110,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brana Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503562.9297659012</v>
+        <v>503495</v>
       </c>
       <c r="R6" t="n">
-        <v>7008437.07306868</v>
+        <v>7008412</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,22 +1151,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,81 +1171,64 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Thomas Stålhandske, Pär Hedberg, Pontus Wallén, Johan Staaf, Erik Lundmark, Eva Romell, Sarah J Leander, Lisa Linck, Maria Gylle, Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102887224</v>
+        <v>109531185</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brana Ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503516.8563916786</v>
+        <v>503481</v>
       </c>
       <c r="R7" t="n">
-        <v>7008425.291131906</v>
+        <v>7008420</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,27 +1252,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Endast räknat blommande/överblommade ex.</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,85 +1266,63 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Thomas Stålhandske, Pär Hedberg, Pontus Wallén, Johan Staaf, Erik Lundmark, Eva Romell, Sarah J Leander, Lisa Linck, Maria Gylle, Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102887215</v>
+        <v>101818225</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brana Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503532.6372460596</v>
+        <v>503474</v>
       </c>
       <c r="R8" t="n">
-        <v>7008455.539238772</v>
+        <v>7008447</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1521,27 +1349,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Endast räknat blommande/överblommade ex.</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,7 +1363,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1569,15 +1381,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109531178</v>
+        <v>101818218</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,41 +1392,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brana Ö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503521.8299306054</v>
+        <v>503463</v>
       </c>
       <c r="R9" t="n">
-        <v>7008422.138087351</v>
+        <v>7008471</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1643,22 +1446,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,49 +1466,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske, Pär Hedberg, Pontus Wallén, Johan Staaf, Erik Lundmark, Eva Romell, Sarah J Leander, Lisa Linck, Maria Gylle, Maria Noro-Larsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109531179</v>
+        <v>101818220</v>
       </c>
       <c r="B10" t="n">
-        <v>95572</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1725,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503516.8681880152</v>
+        <v>503519</v>
       </c>
       <c r="R10" t="n">
-        <v>7008414.462105003</v>
+        <v>7008271</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1755,22 +1543,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1785,66 +1563,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske, Pär Hedberg, Pontus Wallén, Johan Staaf, Erik Lundmark, Eva Romell, Sarah J Leander, Lisa Linck, Maria Gylle, Maria Noro-Larsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103956827</v>
+        <v>101818221</v>
       </c>
       <c r="B11" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brana Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503492.0137328925</v>
+        <v>503566</v>
       </c>
       <c r="R11" t="n">
-        <v>7008418.044809995</v>
+        <v>7008254</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1871,27 +1640,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Område med minst 10 stånd.</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,7 +1654,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1912,44 +1665,39 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Johan Råghall</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109531176</v>
+        <v>102887226</v>
       </c>
       <c r="B12" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1959,13 +1707,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503488.8392366802</v>
+        <v>503488</v>
       </c>
       <c r="R12" t="n">
-        <v>7008428.870405483</v>
+        <v>7008224</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1989,22 +1737,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2019,49 +1757,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske, Pär Hedberg, Pontus Wallén, Johan Staaf, Erik Lundmark, Eva Romell, Sarah J Leander, Lisa Linck, Maria Gylle, Maria Noro-Larsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109531173</v>
+        <v>102887195</v>
       </c>
       <c r="B13" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2071,13 +1804,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503496.0826251701</v>
+        <v>503559</v>
       </c>
       <c r="R13" t="n">
-        <v>7008415.793161616</v>
+        <v>7008406</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2101,22 +1834,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2131,62 +1854,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske, Pär Hedberg, Pontus Wallén, Johan Staaf, Erik Lundmark, Eva Romell, Sarah J Leander, Lisa Linck, Maria Gylle, Maria Noro-Larsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123451766</v>
+        <v>102887196</v>
       </c>
       <c r="B14" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Branaflons SO-spets, i granskog med dike 520 m OSO om, Jmt</t>
+          <t>Brana Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503506</v>
+        <v>503576</v>
       </c>
       <c r="R14" t="n">
-        <v>7008293</v>
+        <v>7008392</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2213,17 +1931,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1993-06-24</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1993-06-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikstaxruta 19F2c13</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2238,15 +1951,1573 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127347858</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>brana ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>503581</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7008471</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>102887191</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Brana Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>503553</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7008380</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>102887206</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Brana Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>503468</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7008492</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Endast räknat blommande/överblommade ex.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>102887207</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brana Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>503475</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7008485</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Endast räknat blommande/överblommade ex.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>102887208</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Brana Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>503503</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7008527</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Endast räknat blommande/överblommade ex.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>102887209</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brana Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>503500</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7008499</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Endast räknat blommande/överblommade ex.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>102887213</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Brana Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>503568</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7008400</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Endast räknat blommande/överblommade ex.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>102887214</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Brana Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>503561</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7008418</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Endast räknat blommande/överblommade ex.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>102887215</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Brana Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>503532</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7008455</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Endast räknat blommande/överblommade ex.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>102887224</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Brana Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>503517</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7008425</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Endast räknat blommande/överblommade ex.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>109531178</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Brana Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>503522</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7008422</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske, Pär Hedberg, Pontus Wallén, Johan Staaf, Erik Lundmark, Eva Romell, Sarah J Leander, Lisa Linck, Maria Gylle, Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>109531179</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98030</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Brana Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>503517</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7008414</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske, Pär Hedberg, Pontus Wallén, Johan Staaf, Erik Lundmark, Eva Romell, Sarah J Leander, Lisa Linck, Maria Gylle, Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>102887194</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Brana Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>503563</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7008437</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>123451766</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Branaflons SO-spets, i granskog med dike 520 m OSO om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>503506</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7008293</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19F2c13</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Staffan Åström</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>Lars-Åke Bäckström</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47392-2022 artfynd.xlsx
+++ b/artfynd/A 47392-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103956827</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109531173</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109531176</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109531177</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109531184</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109531185</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1378,6 +1413,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101818225</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1475,6 +1515,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101818218</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1572,6 +1617,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101818220</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,6 +1719,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101818221</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1766,6 +1821,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887226</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1863,6 +1923,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887195</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1960,6 +2025,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887196</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2072,6 +2142,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347858</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2169,6 +2244,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887191</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887206</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2407,6 +2492,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887207</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2526,6 +2616,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887208</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2645,6 +2740,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887209</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2764,6 +2864,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887213</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2883,6 +2988,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887214</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3002,6 +3112,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887215</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3121,6 +3236,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887224</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3222,6 +3342,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109531178</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3319,6 +3444,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109531179</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3416,6 +3546,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887194</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3518,8 +3653,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123451766</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>